--- a/data_extactor/batch_10_fa/trimmed/batch_0088_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0088_fa_trim.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>نظارت | درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | دقت در کنترل | حساسیت به مسئله | ثبات دست و بازو | چابکی دستی | چابکی انگشتان | تمایز رنگ بصری</t>
+          <t>بینایی نزدیک | دقت کنترل | حساسیت به مسئله | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>متصدیان و اپراتورهای ماشین‌های اتصال چسبی | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورهای ماشین‌های اداری، به‌جز رایانه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تولید محصولات کاغذی | تکنسین‌ها و کارگران لیتوگرافی و پیش از چاپ | کارگران صحافی و تکمیل چاپ</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورهای ماشین‌آلات اداری، به‌جز رایانه | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تکنسین‌ها و کارگران لیتوگرافی و پیش از چاپ | کارگران صحافی و تکمیل چاپ</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -570,12 +570,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | تولید و فرآوری | مکانیک | خدمات مشتریان و خدمات فردی</t>
+          <t>مدیریت و اداره | تولید و فرآوری | مکانیک | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی انگشتان | حساسیت به مسئله | چابکی دستی | ثبات دست و بازو | دقت در کنترل | توجه انتخابی</t>
+          <t>بینایی نزدیک | مهارت انگشتان | حساسیت به مسئله | مهارت دستی | ثبات دست و بازو | دقت کنترل | توجه انتخابی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>متصدیان و اپراتورهای ماشین‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تولید محصولات کاغذی | اپراتورهای ماشین‌های چاپ | اپراتورها و متصدیان ماشین‌آلات کفش | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش پارچه و منسوجات</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | اپراتورهای ماشین‌های چاپ | اپراتورها و متصدیان ماشین‌آلات کفش | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال</t>
+          <t>نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید و فرآوری</t>
+          <t>خدمات مشتری و شخصی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دید نزدیک | دقت در کنترل | چابکی دستی | بیان شفاهی | درک شفاهی | تشخیص گفتار</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | دقت کنترل | مهارت دستی | بیان شفاهی | درک شفاهی | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ظرف‌شویان | سرایداران و نظافتچی‌ها، به‌جز خدمتکاران و نظافتچی‌های هتل و خانه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | خدمتکاران و نظافتچی‌های هتل و اماکن | بسته‌بندها و جعبه‌بندهای دستی | اتوکاران منسوجات، پوشاک و مواد وابسته | چرخکاران صنعتی</t>
+          <t>ظرف‌شویان | سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | خدمتکاران و نظافتچیان منازل و هتل‌ها | کارگران بسته‌بندی دستی | اتوکاران منسوجات، پوشاک و مواد وابسته | چرخکاران صنعتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>نرم‌افزار Microsoft Excel | نرم‌افزار Microsoft Word | نرم‌افزار ایمیل</t>
+          <t>نرم‌افزار ایمیل | نرم‌افزار Microsoft Word</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید و فرآوری</t>
+          <t>خدمات مشتری و شخصی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>چابکی دستی | ثبات دست و بازو | دقت در کنترل | دید نزدیک | هماهنگی اندام‌ها | چابکی انگشتان | قدرت تنه</t>
+          <t>مهارت دستی | ثبات دست و بازو | دقت کنترل | بینایی نزدیک | هماهنگی چند عضو | مهارت انگشتان | قدرت تنه</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کارگران خشکشویی و رختشویخانه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | بسته‌بندها و جعبه‌بندهای دستی | دوزندگان دستی | چرخکاران صنعتی | کارگران و تعمیرکاران کفش و چرم | خیاطان و دوزندگان سفارشی</t>
+          <t>کارگران خشکشویی و رختشویخانه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران بسته‌بندی دستی | دوزندگان دستی | چرخکاران صنعتی | کارگران و تعمیرکاران کفش و چرم | خیاطان و دوزندگان سفارشی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Excel | نرم‌افزار Microsoft Word | نرم‌افزار Microsoft Outlook | نرم‌افزار مرورگر وب | نرم‌افزار ایمیل</t>
+          <t>نرم‌افزار ایمیل | نرم‌افزار Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Outlook | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | طراحی | زبان انگلیسی | ریاضیات | خدمات مشتریان و خدمات فردی</t>
+          <t>تولید و فرآوری | مکانیک | طراحی | زبان انگلیسی | ریاضیات | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی دستی | دقت در کنترل | دید نزدیک | چابکی انگشتان | هماهنگی اندام‌ها | تمایز رنگ بصری</t>
+          <t>ثبات دست و بازو | مهارت دستی | دقت کنترل | بینایی نزدیک | مهارت انگشتان | هماهنگی چند عضو | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>برش‌کاران و پیراسته‌کاران دستی | کارگران خشکشویی و رختشویخانه | اتوکاران منسوجات، پوشاک و مواد وابسته | دوزندگان دستی | کارگران و تعمیرکاران کفش و چرم | خیاطان و دوزندگان سفارشی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش پارچه و منسوجات</t>
+          <t>برشکاران و پیرایشگران دستی | کارگران خشکشویی و رختشویخانه | اتوکاران منسوجات، پوشاک و مواد وابسته | دوزندگان دستی | کارگران و تعمیرکاران کفش و چرم | خیاطان و دوزندگان سفارشی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>نرم‌افزار حسابداری مالی | نرم‌افزار دفترداری | نرم‌افزار ردیابی موجودی | نرم‌افزار پردازش فروش | نرم‌افزار Microsoft Excel</t>
+          <t>نرم‌افزار حسابداری | نرم‌افزار دفترداری | نرم‌افزار ردیابی موجودی | نرم‌افزار پردازش فروش | نرم‌افزار Microsoft Excel</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دید نزدیک | ثبات دست و بازو | چابکی انگشتان | حساسیت به مسئله | دقت در کنترل | چابکی دستی | تجسم فضایی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت انگشتان | حساسیت به مسئله | دقت کنترل | مهارت دستی | تجسم</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>برش‌کاران و پیراسته‌کاران دستی | جواهرسازان و سازندگان مصنوعات فلزات و سنگ‌های قیمتی | دوزندگان دستی | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | خیاطان و دوزندگان سفارشی | رویه‌کوبان مبل و روکش‌کاران</t>
+          <t>برشکاران و پیرایشگران دستی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | دوزندگان دستی | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | خیاطان و دوزندگان سفارشی | رویه‌کوبان و مبل‌کوبان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,22 +845,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | نرم‌افزار کنترل تولید | نرم‌افزار ردیابی موجودی | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Excel | نرم‌افزار Microsoft Word | نرم‌افزار Microsoft PowerPoint | نرم‌افزار Microsoft Outlook</t>
+          <t>Adobe Acrobat | نرم‌افزار کنترل تولید | نرم‌افزار ردیابی موجودی | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Excel | نرم‌افزار Microsoft Word | نرم‌افزار Microsoft PowerPoint | Production control software</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مدیریت و امور اداری</t>
+          <t>تولید و فرآوری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | ثبات دست و بازو | دقت در کنترل | چابکی انگشتان | چابکی دستی | سرعت ادراک | حساسیت به مسئله</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | دقت کنترل | مهارت انگشتان | مهارت دستی | سرعت ادراکی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متصدیان و اپراتورهای ماشین‌های اتصال چسبی | برش‌کاران و پیراسته‌کاران دستی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اتوکاران منسوجات، پوشاک و مواد وابسته | دوزندگان دستی | چرخکاران صنعتی | کارگران و تعمیرکاران کفش و چرم</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | برشکاران و پیرایشگران دستی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اتوکاران منسوجات، پوشاک و مواد وابسته | دوزندگان دستی | چرخکاران صنعتی | کارگران و تعمیرکاران کفش و چرم</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | دید نزدیک | دقت در کنترل | تجسم فضایی | تمایز رنگ بصری</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | بینایی نزدیک | دقت کنترل | تجسم | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>برش‌کاران و پیراسته‌کاران دستی | الگوسازان پارچه و پوشاک | اتوکاران منسوجات، پوشاک و مواد وابسته | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | خیاطان و دوزندگان سفارشی | رویه‌کوبان مبل و روکش‌کاران</t>
+          <t>برشکاران و پیرایشگران دستی | الگوسازان پارچه و پوشاک | اتوکاران منسوجات، پوشاک و مواد وابسته | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | خیاطان و دوزندگان سفارشی | رویه‌کوبان و مبل‌کوبان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | تولید و فرآوری | مدیریت و امور اداری | اقتصاد و حسابداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | تولید و فرآوری | مدیریت و اداره | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>تجسم فضایی | ثبات دست و بازو | چابکی انگشتان | دید نزدیک | دقت در کنترل | چابکی دستی | ابتکار و اصالت</t>
+          <t>تجسم | ثبات دست و بازو | مهارت انگشتان | بینایی نزدیک | دقت کنترل | مهارت دستی | اصالت</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>برش‌کاران و پیراسته‌کاران دستی | الگوسازان پارچه و پوشاک | طراحان مد و لباس | اتوکاران منسوجات، پوشاک و مواد وابسته | دوزندگان دستی | چرخکاران صنعتی | رویه‌کوبان مبل و روکش‌کاران</t>
+          <t>برشکاران و پیرایشگران دستی | الگوسازان پارچه و پوشاک | طراحان مد و پوشاک | اتوکاران منسوجات، پوشاک و مواد وابسته | دوزندگان دستی | چرخکاران صنعتی | رویه‌کوبان و مبل‌کوبان</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال</t>
+          <t>نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دقت در کنترل | دید نزدیک | تمایز رنگ بصری | چابکی دستی | کنترل نرخ حرکت | توجه انتخابی</t>
+          <t>ثبات دست و بازو | دقت کنترل | بینایی نزدیک | تشخیص رنگ بصری | مهارت دستی | کنترل نرخ | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و فرم‌دهی الیاف مصنوعی و شیشه | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌ها | کارگران خشکشویی و رختشویخانه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش پارچه و منسوجات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های بافندگی و تریکوبافی نساجی</t>
+          <t>تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | کارگران خشکشویی و رختشویخانه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بافندگی و تریکوبافی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
